--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484029_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484029_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.427</v>
+        <v>9.6256</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9289</v>
+        <v>5.1556</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4981</v>
+        <v>4.47</v>
       </c>
       <c r="G2" t="n">
         <v>5.2724</v>
@@ -610,13 +610,13 @@
         <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4801</v>
+        <v>0.6787</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4307</v>
+        <v>-0.2039</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9107</v>
+        <v>0.8827</v>
       </c>
       <c r="V2" t="n">
         <v>2.4842</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>P. CAMÍ GALERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7659</v>
+        <v>5.2397</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5463</v>
+        <v>1.442</v>
       </c>
       <c r="F3" t="n">
-        <v>5.3121</v>
+        <v>3.7977</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9474</v>
+        <v>4.9968</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6403</v>
+        <v>-0.5896</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3071</v>
+        <v>5.5864</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5339</v>
+        <v>4.0104</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5454</v>
+        <v>-1.0123</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.0793</v>
+        <v>5.0228</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4813</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0949</v>
+        <v>0.4228</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3864</v>
+        <v>0.5637</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5952</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.9758</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3806</v>
+        <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6157</v>
+        <v>0.9012</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1654</v>
+        <v>-0.1246</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4503</v>
+        <v>1.0258</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.532</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.532</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. CAMÍ GALERA</t>
+          <t>X. ANDREU GARI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5028</v>
+        <v>3.421</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7050999999999999</v>
+        <v>-1.8701</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7977</v>
+        <v>5.2911</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9968</v>
+        <v>3.4281</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5896</v>
+        <v>2.1819</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5864</v>
+        <v>1.2462</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0104</v>
+        <v>1.355</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.0123</v>
+        <v>1.6182</v>
       </c>
       <c r="L4" t="n">
-        <v>5.0228</v>
+        <v>-0.2633</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9864000000000001</v>
+        <v>2.0731</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4228</v>
+        <v>0.5637</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5637</v>
+        <v>1.5094</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1903</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.9758</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>2.1822</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1643</v>
+        <v>0.1119</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8615</v>
+        <v>-0.2493</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0258</v>
+        <v>0.3612</v>
       </c>
       <c r="V4" t="n">
-        <v>0.532</v>
+        <v>0.6745</v>
       </c>
       <c r="W4" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. ANDREU GARI</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4877</v>
+        <v>2.5148</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.607</v>
+        <v>-2.3204</v>
       </c>
       <c r="F5" t="n">
-        <v>5.0947</v>
+        <v>4.8352</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4281</v>
+        <v>0.9474</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1819</v>
+        <v>0.6403</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2462</v>
+        <v>0.3071</v>
       </c>
       <c r="J5" t="n">
-        <v>1.355</v>
+        <v>-0.5339</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6182</v>
+        <v>0.5454</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2633</v>
+        <v>-1.0793</v>
       </c>
       <c r="M5" t="n">
-        <v>2.0731</v>
+        <v>1.4813</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5637</v>
+        <v>0.0949</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5094</v>
+        <v>1.3864</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7935</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.9758</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1822</v>
+        <v>2.3806</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8213</v>
+        <v>1.3646</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9862</v>
+        <v>0.3912</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1648</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6745</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. FLUXA PAYERAS</t>
+          <t>J. RIERA MESTRE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6</v>
+        <v>1.025</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1386</v>
+        <v>-0.3232</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7386</v>
+        <v>1.3483</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2501</v>
+        <v>-0.3636</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1411</v>
+        <v>-0.58</v>
       </c>
       <c r="I6" t="n">
-        <v>1.109</v>
+        <v>0.2164</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2274</v>
+        <v>0.0054</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3374</v>
+        <v>0.0806</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5648</v>
+        <v>-0.0752</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0227</v>
+        <v>-0.3691</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4786</v>
+        <v>-0.6607</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5442</v>
+        <v>0.2916</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5952</v>
+        <v>1.5871</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2534</v>
+        <v>-0.1984</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3741</v>
+        <v>-0.3287</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1207</v>
+        <v>0.1303</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SERRA CASTILLO</t>
+          <t>P. FLUXA PAYERAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5603</v>
+        <v>0.6904</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0237</v>
+        <v>-1.0763</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5839</v>
+        <v>1.7666</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7789</v>
+        <v>1.2501</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2472</v>
+        <v>0.1411</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0261</v>
+        <v>1.109</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6856</v>
+        <v>0.2274</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0806</v>
+        <v>-0.3374</v>
       </c>
       <c r="L7" t="n">
-        <v>0.605</v>
+        <v>0.5648</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09320000000000001</v>
+        <v>1.0227</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3279</v>
+        <v>0.4786</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4211</v>
+        <v>0.5442</v>
       </c>
       <c r="P7" t="n">
         <v>-0.3968</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5871</v>
+        <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4251</v>
+        <v>-0.163</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.3117</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4932</v>
+        <v>0.1488</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RIERA MESTRE</t>
+          <t>J. SERRA CASTILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5047</v>
+        <v>0.6367</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7314000000000001</v>
+        <v>-0.2277</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2361</v>
+        <v>0.8645</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3636</v>
+        <v>0.7789</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.58</v>
+        <v>-0.2472</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2164</v>
+        <v>1.0261</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0054</v>
+        <v>0.6856</v>
       </c>
       <c r="K8" t="n">
         <v>0.0806</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0752</v>
+        <v>0.605</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3691</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6607</v>
+        <v>-0.3279</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2916</v>
+        <v>0.4211</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5871</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R8" t="n">
         <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7187</v>
+        <v>-0.3486</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7368</v>
+        <v>-0.136</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0181</v>
+        <v>-0.2126</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.666</v>
+        <v>-1.7948</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3708</v>
+        <v>-3.0226</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7047</v>
+        <v>1.2278</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0371</v>
@@ -1156,13 +1156,13 @@
         <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5695</v>
+        <v>0.4407</v>
       </c>
       <c r="T9" t="n">
-        <v>0.873</v>
+        <v>0.2211</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6965</v>
+        <v>0.2196</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6032</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.188</v>
+        <v>-1.7978</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5524</v>
+        <v>-3.2463</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3643</v>
+        <v>1.4485</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6291</v>
@@ -1234,13 +1234,13 @@
         <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6978</v>
+        <v>-0.3075</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6858</v>
+        <v>-0.3797</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.012</v>
+        <v>0.0722</v>
       </c>
       <c r="V10" t="n">
         <v>-0.266</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2677</v>
+        <v>-2.9157</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2968</v>
+        <v>-3.8887</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0291</v>
+        <v>0.973</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5193</v>
@@ -1312,13 +1312,13 @@
         <v>1.7855</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9387</v>
+        <v>-0.5867</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6121</v>
+        <v>-0.204</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3266</v>
+        <v>-0.3827</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6032</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6658</v>
+        <v>-2.9607</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.4516</v>
+        <v>-5.0831</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7858</v>
+        <v>2.1225</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9947</v>
@@ -1390,13 +1390,13 @@
         <v>2.9758</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4727</v>
+        <v>0.2324</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2323</v>
+        <v>0.1361</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2404</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2065</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.0609</v>
+        <v>13.6842</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.0846</v>
+        <v>-14.4608</v>
       </c>
       <c r="F13" t="n">
-        <v>28.1451</v>
+        <v>28.1452</v>
       </c>
       <c r="G13" t="n">
         <v>11.1299</v>
@@ -1468,13 +1468,13 @@
         <v>18.8467</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5019</v>
+        <v>2.1253</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.813</v>
+        <v>-1.1895</v>
       </c>
       <c r="U13" t="n">
-        <v>3.314699999999999</v>
+        <v>3.314800000000001</v>
       </c>
       <c r="V13" t="n">
         <v>2.4129</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. FIGUERAS GÜELL</t>
+          <t>J. CAÑELLAS VAQUÉ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.472</v>
+        <v>2.1461</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5516</v>
+        <v>0.0449</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9204</v>
+        <v>2.1012</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7419</v>
+        <v>0.6442</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2871</v>
+        <v>0.705</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4548</v>
+        <v>-0.0608</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1208</v>
+        <v>0.5266</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0806</v>
+        <v>0.4839</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0402</v>
+        <v>0.0427</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6211</v>
+        <v>0.1176</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2065</v>
+        <v>0.2212</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4146</v>
+        <v>-0.1035</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5952</v>
+        <v>2.7774</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5952</v>
+        <v>2.7774</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1349</v>
+        <v>-0.1403</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4308</v>
+        <v>-0.4817</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2959</v>
+        <v>0.3414</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-1.1352</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CAÑELLAS VAQUÉ</t>
+          <t>A. FIGUERAS GÜELL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3902</v>
+        <v>1.4703</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7713</v>
+        <v>0.2455</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1615</v>
+        <v>1.2247</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6442</v>
+        <v>0.7419</v>
       </c>
       <c r="H15" t="n">
-        <v>0.705</v>
+        <v>0.2871</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0608</v>
+        <v>0.4548</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5266</v>
+        <v>0.1208</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4839</v>
+        <v>0.0806</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0427</v>
+        <v>0.0402</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1176</v>
+        <v>0.6211</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2212</v>
+        <v>0.2065</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1035</v>
+        <v>0.4146</v>
       </c>
       <c r="P15" t="n">
-        <v>2.7774</v>
+        <v>0.5952</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7774</v>
+        <v>0.5952</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8962</v>
+        <v>0.1332</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2979</v>
+        <v>0.1247</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4017</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.1352</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.049</v>
+        <v>0.2116</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.8682</v>
+        <v>-4.2763</v>
       </c>
       <c r="F16" t="n">
-        <v>4.9172</v>
+        <v>4.4879</v>
       </c>
       <c r="G16" t="n">
         <v>-3.1441</v>
@@ -1702,13 +1702,13 @@
         <v>4.1661</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0741</v>
+        <v>0.2367</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2038</v>
+        <v>-0.612</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2779</v>
+        <v>0.8486</v>
       </c>
       <c r="V16" t="n">
         <v>1.1352</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5226</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5957</v>
+        <v>-2.1262</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1184</v>
+        <v>1.5027</v>
       </c>
       <c r="G17" t="n">
         <v>2.7619</v>
@@ -1780,13 +1780,13 @@
         <v>3.3725</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3559</v>
+        <v>0.2098</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6043</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2484</v>
+        <v>0.1359</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8097</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4239</v>
+        <v>-1.5856</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.3951</v>
+        <v>-3.8849</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9712</v>
+        <v>2.2993</v>
       </c>
       <c r="G18" t="n">
         <v>-2.3763</v>
@@ -1858,13 +1858,13 @@
         <v>2.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0396</v>
+        <v>-0.2012</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9125</v>
+        <v>-0.4023</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1271</v>
+        <v>0.2011</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6519</v>
+        <v>-2.4317</v>
       </c>
       <c r="E19" t="n">
         <v>-6.1665</v>
       </c>
       <c r="F19" t="n">
-        <v>3.5146</v>
+        <v>3.7348</v>
       </c>
       <c r="G19" t="n">
         <v>-3.6708</v>
@@ -1936,13 +1936,13 @@
         <v>2.579</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0902</v>
+        <v>0.3104</v>
       </c>
       <c r="T19" t="n">
         <v>-0.7934</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8835</v>
+        <v>1.1038</v>
       </c>
       <c r="V19" t="n">
         <v>0.532</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0828</v>
+        <v>-3.4987</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0294</v>
+        <v>-3.4173</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0533</v>
+        <v>-0.0814</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4179</v>
@@ -2014,13 +2014,13 @@
         <v>2.579</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8632</v>
+        <v>-0.2791</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4736</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6103</v>
+        <v>0.5823</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2065</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.3361</v>
+        <v>-7.389</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.8706</v>
+        <v>-8.564500000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5345</v>
+        <v>1.1755</v>
       </c>
       <c r="G21" t="n">
         <v>-4.6688</v>
@@ -2092,13 +2092,13 @@
         <v>2.579</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.358</v>
+        <v>-0.4109</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6687</v>
+        <v>-0.3626</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6893</v>
+        <v>-0.0483</v>
       </c>
       <c r="V21" t="n">
         <v>0.0713</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-13.0609</v>
+        <v>-11.7005</v>
       </c>
       <c r="E22" t="n">
-        <v>-28.1452</v>
+        <v>-28.1453</v>
       </c>
       <c r="F22" t="n">
-        <v>15.0845</v>
+        <v>16.4447</v>
       </c>
       <c r="G22" t="n">
         <v>-11.1299</v>
@@ -2170,13 +2170,13 @@
         <v>20.8304</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5019</v>
+        <v>-0.1414</v>
       </c>
       <c r="T22" t="n">
         <v>-3.3148</v>
       </c>
       <c r="U22" t="n">
-        <v>1.8127</v>
+        <v>3.1733</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4129</v>
